--- a/ws.xlsx
+++ b/ws.xlsx
@@ -23,6 +23,47 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>HYD</t>
+  </si>
+  <si>
+    <t>ELI</t>
+  </si>
+  <si>
+    <t>EIC</t>
+  </si>
+  <si>
+    <t>ENG</t>
+  </si>
+  <si>
+    <t>COO</t>
+  </si>
+  <si>
+    <t>STRU</t>
+  </si>
+  <si>
+    <t>LSTRU</t>
+  </si>
+  <si>
+    <t>ESI</t>
+  </si>
+  <si>
+    <t>CAB</t>
+  </si>
+  <si>
+    <t>Start Date</t>
+  </si>
+  <si>
+    <t>End Date</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
@@ -34,12 +75,72 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF000000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF00FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00AA66"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0066AA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA6600"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3333FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -54,8 +155,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -370,9 +482,1358 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B9854BD-A2A3-4494-AC62-9F60ECB6DEA5}">
-  <dimension ref="A1"/>
+  <dimension ref="B1:PB12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="6" max="423" width="1.77734375" customWidth="1"/>
+    <col min="424" max="424" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="426" max="426" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="428" max="428" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="430" max="430" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="432" max="432" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="434" max="434" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="436" max="436" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="438" max="438" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="440" max="440" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="442" max="442" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="444" max="444" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="446" max="446" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="448" max="448" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="450" max="450" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="452" max="452" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="454" max="454" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="456" max="456" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="458" max="458" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="460" max="460" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="462" max="462" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="464" max="464" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="466" max="466" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="468" max="468" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="470" max="470" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="472" max="472" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="474" max="474" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="476" max="476" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="478" max="478" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="480" max="480" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="482" max="482" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="484" max="484" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="486" max="486" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="488" max="488" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="490" max="490" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="492" max="492" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="494" max="494" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="496" max="496" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="498" max="498" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="500" max="500" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="502" max="502" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="504" max="504" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="506" max="506" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="508" max="508" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="510" max="510" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="512" max="512" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="514" max="514" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="516" max="516" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="518" max="518" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="520" max="520" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="522" max="522" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="524" max="524" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="526" max="526" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="528" max="528" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="530" max="530" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="532" max="532" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="534" max="534" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="536" max="536" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="538" max="538" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="540" max="540" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="542" max="542" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="544" max="544" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="546" max="546" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="548" max="548" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="550" max="550" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="552" max="552" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="554" max="554" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="556" max="556" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="558" max="558" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="560" max="560" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="562" max="562" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="564" max="564" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="566" max="566" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="568" max="568" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="570" max="570" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="572" max="572" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="574" max="574" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="576" max="576" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="578" max="578" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="580" max="580" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="582" max="582" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="584" max="584" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="586" max="586" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="588" max="588" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="590" max="590" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="592" max="592" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="594" max="594" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="596" max="596" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="598" max="598" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="600" max="600" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="602" max="602" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="604" max="604" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="606" max="606" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="608" max="608" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="610" max="610" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="612" max="612" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="614" max="614" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="616" max="616" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="618" max="618" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="620" max="620" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="622" max="622" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="624" max="624" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="626" max="626" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="628" max="628" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="630" max="630" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="632" max="632" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="634" max="634" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="636" max="636" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="638" max="638" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="640" max="640" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="642" max="642" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="644" max="644" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="646" max="646" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="648" max="648" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="650" max="650" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="652" max="652" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="654" max="654" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="656" max="656" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="658" max="658" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="660" max="660" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="662" max="662" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="664" max="664" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="666" max="666" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="668" max="668" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="670" max="670" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="672" max="672" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="674" max="674" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="676" max="676" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="678" max="678" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="680" max="680" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="682" max="682" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="684" max="684" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="686" max="686" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="688" max="688" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="690" max="690" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="692" max="692" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="694" max="694" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="696" max="696" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="698" max="698" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="700" max="700" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="702" max="702" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="704" max="704" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="706" max="706" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="708" max="708" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="710" max="710" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="712" max="712" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="714" max="714" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="716" max="716" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="718" max="718" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="720" max="720" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="722" max="722" width="10.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:418" x14ac:dyDescent="0.3">
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="1">
+        <v>43469</v>
+      </c>
+      <c r="G1" s="1">
+        <v>43470</v>
+      </c>
+      <c r="H1" s="1">
+        <v>43471</v>
+      </c>
+      <c r="I1" s="1">
+        <v>43472</v>
+      </c>
+      <c r="J1" s="1">
+        <v>43473</v>
+      </c>
+      <c r="K1" s="1">
+        <v>43474</v>
+      </c>
+      <c r="L1" s="1">
+        <v>43475</v>
+      </c>
+      <c r="M1" s="3"/>
+      <c r="N1" s="1">
+        <v>43476</v>
+      </c>
+      <c r="O1" s="1">
+        <v>43477</v>
+      </c>
+      <c r="P1" s="1">
+        <v>43478</v>
+      </c>
+      <c r="Q1" s="1">
+        <v>43479</v>
+      </c>
+      <c r="R1" s="1">
+        <v>43480</v>
+      </c>
+      <c r="S1" s="1">
+        <v>43481</v>
+      </c>
+      <c r="T1" s="1">
+        <v>43482</v>
+      </c>
+      <c r="U1" s="3"/>
+      <c r="V1" s="1">
+        <v>43483</v>
+      </c>
+      <c r="W1" s="1">
+        <v>43484</v>
+      </c>
+      <c r="X1" s="1">
+        <v>43485</v>
+      </c>
+      <c r="Y1" s="1">
+        <v>43486</v>
+      </c>
+      <c r="Z1" s="1">
+        <v>43487</v>
+      </c>
+      <c r="AA1" s="1">
+        <v>43488</v>
+      </c>
+      <c r="AB1" s="1">
+        <v>43489</v>
+      </c>
+      <c r="AC1" s="3"/>
+      <c r="AD1" s="1">
+        <v>43490</v>
+      </c>
+      <c r="AE1" s="1">
+        <v>43491</v>
+      </c>
+      <c r="AF1" s="1">
+        <v>43492</v>
+      </c>
+      <c r="AG1" s="1">
+        <v>43493</v>
+      </c>
+      <c r="AH1" s="1">
+        <v>43494</v>
+      </c>
+      <c r="AI1" s="1">
+        <v>43495</v>
+      </c>
+      <c r="AJ1" s="1">
+        <v>43496</v>
+      </c>
+      <c r="AK1" s="3"/>
+      <c r="AL1" s="1">
+        <v>43497</v>
+      </c>
+      <c r="AM1" s="1">
+        <v>43498</v>
+      </c>
+      <c r="AN1" s="1">
+        <v>43499</v>
+      </c>
+      <c r="AO1" s="1">
+        <v>43500</v>
+      </c>
+      <c r="AP1" s="1">
+        <v>43501</v>
+      </c>
+      <c r="AQ1" s="1">
+        <v>43502</v>
+      </c>
+      <c r="AR1" s="1">
+        <v>43503</v>
+      </c>
+      <c r="AS1" s="3"/>
+      <c r="AT1" s="1">
+        <v>43504</v>
+      </c>
+      <c r="AU1" s="1">
+        <v>43505</v>
+      </c>
+      <c r="AV1" s="1">
+        <v>43506</v>
+      </c>
+      <c r="AW1" s="1">
+        <v>43507</v>
+      </c>
+      <c r="AX1" s="1">
+        <v>43508</v>
+      </c>
+      <c r="AY1" s="1">
+        <v>43509</v>
+      </c>
+      <c r="AZ1" s="1">
+        <v>43510</v>
+      </c>
+      <c r="BA1" s="3"/>
+      <c r="BB1" s="1">
+        <v>43511</v>
+      </c>
+      <c r="BC1" s="1">
+        <v>43512</v>
+      </c>
+      <c r="BD1" s="1">
+        <v>43513</v>
+      </c>
+      <c r="BE1" s="1">
+        <v>43514</v>
+      </c>
+      <c r="BF1" s="1">
+        <v>43515</v>
+      </c>
+      <c r="BG1" s="1">
+        <v>43516</v>
+      </c>
+      <c r="BH1" s="1">
+        <v>43517</v>
+      </c>
+      <c r="BI1" s="3"/>
+      <c r="BJ1" s="1">
+        <v>43518</v>
+      </c>
+      <c r="BK1" s="1">
+        <v>43519</v>
+      </c>
+      <c r="BL1" s="1">
+        <v>43520</v>
+      </c>
+      <c r="BM1" s="1">
+        <v>43521</v>
+      </c>
+      <c r="BN1" s="1">
+        <v>43522</v>
+      </c>
+      <c r="BO1" s="1">
+        <v>43523</v>
+      </c>
+      <c r="BP1" s="1">
+        <v>43524</v>
+      </c>
+      <c r="BQ1" s="3"/>
+      <c r="BR1" s="1">
+        <v>43525</v>
+      </c>
+      <c r="BS1" s="1">
+        <v>43526</v>
+      </c>
+      <c r="BT1" s="1">
+        <v>43527</v>
+      </c>
+      <c r="BU1" s="1">
+        <v>43528</v>
+      </c>
+      <c r="BV1" s="1">
+        <v>43529</v>
+      </c>
+      <c r="BW1" s="1">
+        <v>43530</v>
+      </c>
+      <c r="BX1" s="1">
+        <v>43531</v>
+      </c>
+      <c r="BY1" s="3"/>
+      <c r="BZ1" s="1">
+        <v>43532</v>
+      </c>
+      <c r="CA1" s="1">
+        <v>43533</v>
+      </c>
+      <c r="CB1" s="1">
+        <v>43534</v>
+      </c>
+      <c r="CC1" s="1">
+        <v>43535</v>
+      </c>
+      <c r="CD1" s="1">
+        <v>43536</v>
+      </c>
+      <c r="CE1" s="1">
+        <v>43537</v>
+      </c>
+      <c r="CF1" s="1">
+        <v>43538</v>
+      </c>
+      <c r="CG1" s="3"/>
+      <c r="CH1" s="1">
+        <v>43539</v>
+      </c>
+      <c r="CI1" s="1">
+        <v>43540</v>
+      </c>
+      <c r="CJ1" s="1">
+        <v>43541</v>
+      </c>
+      <c r="CK1" s="1">
+        <v>43542</v>
+      </c>
+      <c r="CL1" s="1">
+        <v>43543</v>
+      </c>
+      <c r="CM1" s="1">
+        <v>43544</v>
+      </c>
+      <c r="CN1" s="1">
+        <v>43545</v>
+      </c>
+      <c r="CO1" s="3"/>
+      <c r="CP1" s="1">
+        <v>43546</v>
+      </c>
+      <c r="CQ1" s="1">
+        <v>43547</v>
+      </c>
+      <c r="CR1" s="1">
+        <v>43548</v>
+      </c>
+      <c r="CS1" s="1">
+        <v>43549</v>
+      </c>
+      <c r="CT1" s="1">
+        <v>43550</v>
+      </c>
+      <c r="CU1" s="1">
+        <v>43551</v>
+      </c>
+      <c r="CV1" s="1">
+        <v>43552</v>
+      </c>
+      <c r="CW1" s="3"/>
+      <c r="CX1" s="1">
+        <v>43553</v>
+      </c>
+      <c r="CY1" s="1">
+        <v>43554</v>
+      </c>
+      <c r="CZ1" s="1">
+        <v>43555</v>
+      </c>
+      <c r="DA1" s="1">
+        <v>43556</v>
+      </c>
+      <c r="DB1" s="1">
+        <v>43557</v>
+      </c>
+      <c r="DC1" s="1">
+        <v>43558</v>
+      </c>
+      <c r="DD1" s="1">
+        <v>43559</v>
+      </c>
+      <c r="DE1" s="3"/>
+      <c r="DF1" s="1">
+        <v>43560</v>
+      </c>
+      <c r="DG1" s="1">
+        <v>43561</v>
+      </c>
+      <c r="DH1" s="1">
+        <v>43562</v>
+      </c>
+      <c r="DI1" s="1">
+        <v>43563</v>
+      </c>
+      <c r="DJ1" s="1">
+        <v>43564</v>
+      </c>
+      <c r="DK1" s="1">
+        <v>43565</v>
+      </c>
+      <c r="DL1" s="1">
+        <v>43566</v>
+      </c>
+      <c r="DM1" s="3"/>
+      <c r="DN1" s="1">
+        <v>43567</v>
+      </c>
+      <c r="DO1" s="1">
+        <v>43568</v>
+      </c>
+      <c r="DP1" s="1">
+        <v>43569</v>
+      </c>
+      <c r="DQ1" s="1">
+        <v>43570</v>
+      </c>
+      <c r="DR1" s="1">
+        <v>43571</v>
+      </c>
+      <c r="DS1" s="1">
+        <v>43572</v>
+      </c>
+      <c r="DT1" s="1">
+        <v>43573</v>
+      </c>
+      <c r="DU1" s="3"/>
+      <c r="DV1" s="1">
+        <v>43574</v>
+      </c>
+      <c r="DW1" s="1">
+        <v>43575</v>
+      </c>
+      <c r="DX1" s="1">
+        <v>43576</v>
+      </c>
+      <c r="DY1" s="1">
+        <v>43577</v>
+      </c>
+      <c r="DZ1" s="1">
+        <v>43578</v>
+      </c>
+      <c r="EA1" s="1">
+        <v>43579</v>
+      </c>
+      <c r="EB1" s="1">
+        <v>43580</v>
+      </c>
+      <c r="EC1" s="3"/>
+      <c r="ED1" s="1">
+        <v>43581</v>
+      </c>
+      <c r="EE1" s="1">
+        <v>43582</v>
+      </c>
+      <c r="EF1" s="1">
+        <v>43583</v>
+      </c>
+      <c r="EG1" s="1">
+        <v>43584</v>
+      </c>
+      <c r="EH1" s="1">
+        <v>43585</v>
+      </c>
+      <c r="EI1" s="1">
+        <v>43586</v>
+      </c>
+      <c r="EJ1" s="1">
+        <v>43587</v>
+      </c>
+      <c r="EK1" s="3"/>
+      <c r="EL1" s="1">
+        <v>43588</v>
+      </c>
+      <c r="EM1" s="1">
+        <v>43589</v>
+      </c>
+      <c r="EN1" s="1">
+        <v>43590</v>
+      </c>
+      <c r="EO1" s="1">
+        <v>43591</v>
+      </c>
+      <c r="EP1" s="1">
+        <v>43592</v>
+      </c>
+      <c r="EQ1" s="1">
+        <v>43593</v>
+      </c>
+      <c r="ER1" s="1">
+        <v>43594</v>
+      </c>
+      <c r="ES1" s="3"/>
+      <c r="ET1" s="1">
+        <v>43595</v>
+      </c>
+      <c r="EU1" s="1">
+        <v>43596</v>
+      </c>
+      <c r="EV1" s="1">
+        <v>43597</v>
+      </c>
+      <c r="EW1" s="1">
+        <v>43598</v>
+      </c>
+      <c r="EX1" s="1">
+        <v>43599</v>
+      </c>
+      <c r="EY1" s="1">
+        <v>43600</v>
+      </c>
+      <c r="EZ1" s="1">
+        <v>43601</v>
+      </c>
+      <c r="FA1" s="3"/>
+      <c r="FB1" s="1">
+        <v>43602</v>
+      </c>
+      <c r="FC1" s="1">
+        <v>43603</v>
+      </c>
+      <c r="FD1" s="1">
+        <v>43604</v>
+      </c>
+      <c r="FE1" s="1">
+        <v>43605</v>
+      </c>
+      <c r="FF1" s="1">
+        <v>43606</v>
+      </c>
+      <c r="FG1" s="1">
+        <v>43607</v>
+      </c>
+      <c r="FH1" s="1">
+        <v>43608</v>
+      </c>
+      <c r="FI1" s="3"/>
+      <c r="FJ1" s="1">
+        <v>43609</v>
+      </c>
+      <c r="FK1" s="1">
+        <v>43610</v>
+      </c>
+      <c r="FL1" s="1">
+        <v>43611</v>
+      </c>
+      <c r="FM1" s="1">
+        <v>43612</v>
+      </c>
+      <c r="FN1" s="1">
+        <v>43613</v>
+      </c>
+      <c r="FO1" s="1">
+        <v>43614</v>
+      </c>
+      <c r="FP1" s="1">
+        <v>43615</v>
+      </c>
+      <c r="FQ1" s="3"/>
+      <c r="FR1" s="1">
+        <v>43616</v>
+      </c>
+      <c r="FS1" s="1">
+        <v>43617</v>
+      </c>
+      <c r="FT1" s="1">
+        <v>43618</v>
+      </c>
+      <c r="FU1" s="1">
+        <v>43619</v>
+      </c>
+      <c r="FV1" s="1">
+        <v>43620</v>
+      </c>
+      <c r="FW1" s="1">
+        <v>43621</v>
+      </c>
+      <c r="FX1" s="1">
+        <v>43622</v>
+      </c>
+      <c r="FY1" s="3"/>
+      <c r="FZ1" s="1">
+        <v>43623</v>
+      </c>
+      <c r="GA1" s="1">
+        <v>43624</v>
+      </c>
+      <c r="GB1" s="1">
+        <v>43625</v>
+      </c>
+      <c r="GC1" s="1">
+        <v>43626</v>
+      </c>
+      <c r="GD1" s="1">
+        <v>43627</v>
+      </c>
+      <c r="GE1" s="1">
+        <v>43628</v>
+      </c>
+      <c r="GF1" s="1">
+        <v>43629</v>
+      </c>
+      <c r="GG1" s="3"/>
+      <c r="GH1" s="1">
+        <v>43630</v>
+      </c>
+      <c r="GI1" s="1">
+        <v>43631</v>
+      </c>
+      <c r="GJ1" s="1">
+        <v>43632</v>
+      </c>
+      <c r="GK1" s="1">
+        <v>43633</v>
+      </c>
+      <c r="GL1" s="1">
+        <v>43634</v>
+      </c>
+      <c r="GM1" s="1">
+        <v>43635</v>
+      </c>
+      <c r="GN1" s="1">
+        <v>43636</v>
+      </c>
+      <c r="GO1" s="3"/>
+      <c r="GP1" s="1">
+        <v>43637</v>
+      </c>
+      <c r="GQ1" s="1">
+        <v>43638</v>
+      </c>
+      <c r="GR1" s="1">
+        <v>43639</v>
+      </c>
+      <c r="GS1" s="1">
+        <v>43640</v>
+      </c>
+      <c r="GT1" s="1">
+        <v>43641</v>
+      </c>
+      <c r="GU1" s="1">
+        <v>43642</v>
+      </c>
+      <c r="GV1" s="1">
+        <v>43643</v>
+      </c>
+      <c r="GW1" s="3"/>
+      <c r="GX1" s="1">
+        <v>43644</v>
+      </c>
+      <c r="GY1" s="1">
+        <v>43645</v>
+      </c>
+      <c r="GZ1" s="1">
+        <v>43646</v>
+      </c>
+      <c r="HA1" s="1">
+        <v>43647</v>
+      </c>
+      <c r="HB1" s="1">
+        <v>43648</v>
+      </c>
+      <c r="HC1" s="1">
+        <v>43649</v>
+      </c>
+      <c r="HD1" s="1">
+        <v>43650</v>
+      </c>
+      <c r="HE1" s="3"/>
+      <c r="HF1" s="1">
+        <v>43651</v>
+      </c>
+      <c r="HG1" s="1">
+        <v>43652</v>
+      </c>
+      <c r="HH1" s="1">
+        <v>43653</v>
+      </c>
+      <c r="HI1" s="1">
+        <v>43654</v>
+      </c>
+      <c r="HJ1" s="1">
+        <v>43655</v>
+      </c>
+      <c r="HK1" s="1">
+        <v>43656</v>
+      </c>
+      <c r="HL1" s="1">
+        <v>43657</v>
+      </c>
+      <c r="HM1" s="3"/>
+      <c r="HN1" s="1">
+        <v>43658</v>
+      </c>
+      <c r="HO1" s="1">
+        <v>43659</v>
+      </c>
+      <c r="HP1" s="1">
+        <v>43660</v>
+      </c>
+      <c r="HQ1" s="1">
+        <v>43661</v>
+      </c>
+      <c r="HR1" s="1">
+        <v>43662</v>
+      </c>
+      <c r="HS1" s="1">
+        <v>43663</v>
+      </c>
+      <c r="HT1" s="1">
+        <v>43664</v>
+      </c>
+      <c r="HU1" s="3"/>
+      <c r="HV1" s="1">
+        <v>43665</v>
+      </c>
+      <c r="HW1" s="1">
+        <v>43666</v>
+      </c>
+      <c r="HX1" s="1">
+        <v>43667</v>
+      </c>
+      <c r="HY1" s="1">
+        <v>43668</v>
+      </c>
+      <c r="HZ1" s="1">
+        <v>43669</v>
+      </c>
+      <c r="IA1" s="1">
+        <v>43670</v>
+      </c>
+      <c r="IB1" s="1">
+        <v>43671</v>
+      </c>
+      <c r="IC1" s="3"/>
+      <c r="ID1" s="1">
+        <v>43672</v>
+      </c>
+      <c r="IE1" s="1">
+        <v>43673</v>
+      </c>
+      <c r="IF1" s="1">
+        <v>43674</v>
+      </c>
+      <c r="IG1" s="1">
+        <v>43675</v>
+      </c>
+      <c r="IH1" s="1">
+        <v>43676</v>
+      </c>
+      <c r="II1" s="1">
+        <v>43677</v>
+      </c>
+      <c r="IJ1" s="1">
+        <v>43678</v>
+      </c>
+      <c r="IK1" s="3"/>
+      <c r="IL1" s="1">
+        <v>43679</v>
+      </c>
+      <c r="IM1" s="1">
+        <v>43680</v>
+      </c>
+      <c r="IN1" s="1">
+        <v>43681</v>
+      </c>
+      <c r="IO1" s="1">
+        <v>43682</v>
+      </c>
+      <c r="IP1" s="1">
+        <v>43683</v>
+      </c>
+      <c r="IQ1" s="1">
+        <v>43684</v>
+      </c>
+      <c r="IR1" s="1">
+        <v>43685</v>
+      </c>
+      <c r="IS1" s="3"/>
+      <c r="IT1" s="1">
+        <v>43686</v>
+      </c>
+      <c r="IU1" s="1">
+        <v>43687</v>
+      </c>
+      <c r="IV1" s="1">
+        <v>43688</v>
+      </c>
+      <c r="IW1" s="1">
+        <v>43689</v>
+      </c>
+      <c r="IX1" s="1">
+        <v>43690</v>
+      </c>
+      <c r="IY1" s="1">
+        <v>43691</v>
+      </c>
+      <c r="IZ1" s="1">
+        <v>43692</v>
+      </c>
+      <c r="JA1" s="3"/>
+      <c r="JB1" s="1">
+        <v>43693</v>
+      </c>
+      <c r="JC1" s="1">
+        <v>43694</v>
+      </c>
+      <c r="JD1" s="1">
+        <v>43695</v>
+      </c>
+      <c r="JE1" s="1">
+        <v>43696</v>
+      </c>
+      <c r="JF1" s="1">
+        <v>43697</v>
+      </c>
+      <c r="JG1" s="1">
+        <v>43698</v>
+      </c>
+      <c r="JH1" s="1">
+        <v>43699</v>
+      </c>
+      <c r="JI1" s="3"/>
+      <c r="JJ1" s="1">
+        <v>43700</v>
+      </c>
+      <c r="JK1" s="1">
+        <v>43701</v>
+      </c>
+      <c r="JL1" s="1">
+        <v>43702</v>
+      </c>
+      <c r="JM1" s="1">
+        <v>43703</v>
+      </c>
+      <c r="JN1" s="1">
+        <v>43704</v>
+      </c>
+      <c r="JO1" s="1">
+        <v>43705</v>
+      </c>
+      <c r="JP1" s="1">
+        <v>43706</v>
+      </c>
+      <c r="JQ1" s="3"/>
+      <c r="JR1" s="1">
+        <v>43707</v>
+      </c>
+      <c r="JS1" s="1">
+        <v>43708</v>
+      </c>
+      <c r="JT1" s="1">
+        <v>43709</v>
+      </c>
+      <c r="JU1" s="1">
+        <v>43710</v>
+      </c>
+      <c r="JV1" s="1">
+        <v>43711</v>
+      </c>
+      <c r="JW1" s="1">
+        <v>43712</v>
+      </c>
+      <c r="JX1" s="1">
+        <v>43713</v>
+      </c>
+      <c r="JY1" s="3"/>
+      <c r="JZ1" s="1">
+        <v>43714</v>
+      </c>
+      <c r="KA1" s="1">
+        <v>43715</v>
+      </c>
+      <c r="KB1" s="1">
+        <v>43716</v>
+      </c>
+      <c r="KC1" s="1">
+        <v>43717</v>
+      </c>
+      <c r="KD1" s="1">
+        <v>43718</v>
+      </c>
+      <c r="KE1" s="1">
+        <v>43719</v>
+      </c>
+      <c r="KF1" s="1">
+        <v>43720</v>
+      </c>
+      <c r="KG1" s="3"/>
+      <c r="KH1" s="1">
+        <v>43721</v>
+      </c>
+      <c r="KI1" s="1">
+        <v>43722</v>
+      </c>
+      <c r="KJ1" s="1">
+        <v>43723</v>
+      </c>
+      <c r="KK1" s="1">
+        <v>43724</v>
+      </c>
+      <c r="KL1" s="1">
+        <v>43725</v>
+      </c>
+      <c r="KM1" s="1">
+        <v>43726</v>
+      </c>
+      <c r="KN1" s="1">
+        <v>43727</v>
+      </c>
+      <c r="KO1" s="3"/>
+      <c r="KP1" s="1">
+        <v>43728</v>
+      </c>
+      <c r="KQ1" s="1">
+        <v>43729</v>
+      </c>
+      <c r="KR1" s="1">
+        <v>43730</v>
+      </c>
+      <c r="KS1" s="1">
+        <v>43731</v>
+      </c>
+      <c r="KT1" s="1">
+        <v>43732</v>
+      </c>
+      <c r="KU1" s="1">
+        <v>43733</v>
+      </c>
+      <c r="KV1" s="1">
+        <v>43734</v>
+      </c>
+      <c r="KW1" s="3"/>
+      <c r="KX1" s="1">
+        <v>43735</v>
+      </c>
+      <c r="KY1" s="1">
+        <v>43736</v>
+      </c>
+      <c r="KZ1" s="1">
+        <v>43737</v>
+      </c>
+      <c r="LA1" s="1">
+        <v>43738</v>
+      </c>
+      <c r="LB1" s="1">
+        <v>43739</v>
+      </c>
+      <c r="LC1" s="1">
+        <v>43740</v>
+      </c>
+      <c r="LD1" s="1">
+        <v>43741</v>
+      </c>
+      <c r="LE1" s="3"/>
+      <c r="LF1" s="1">
+        <v>43742</v>
+      </c>
+      <c r="LG1" s="1">
+        <v>43743</v>
+      </c>
+      <c r="LH1" s="1">
+        <v>43744</v>
+      </c>
+      <c r="LI1" s="1">
+        <v>43745</v>
+      </c>
+      <c r="LJ1" s="1">
+        <v>43746</v>
+      </c>
+      <c r="LK1" s="1">
+        <v>43747</v>
+      </c>
+      <c r="LL1" s="1">
+        <v>43748</v>
+      </c>
+      <c r="LM1" s="3"/>
+      <c r="LN1" s="1">
+        <v>43749</v>
+      </c>
+      <c r="LO1" s="1">
+        <v>43750</v>
+      </c>
+      <c r="LP1" s="1">
+        <v>43751</v>
+      </c>
+      <c r="LQ1" s="1">
+        <v>43752</v>
+      </c>
+      <c r="LR1" s="1">
+        <v>43753</v>
+      </c>
+      <c r="LS1" s="1">
+        <v>43754</v>
+      </c>
+      <c r="LT1" s="1">
+        <v>43755</v>
+      </c>
+      <c r="LU1" s="3"/>
+      <c r="LV1" s="1">
+        <v>43756</v>
+      </c>
+      <c r="LW1" s="1">
+        <v>43757</v>
+      </c>
+      <c r="LX1" s="1">
+        <v>43758</v>
+      </c>
+      <c r="LY1" s="1">
+        <v>43759</v>
+      </c>
+      <c r="LZ1" s="1">
+        <v>43760</v>
+      </c>
+      <c r="MA1" s="1">
+        <v>43761</v>
+      </c>
+      <c r="MB1" s="1">
+        <v>43762</v>
+      </c>
+      <c r="MC1" s="3"/>
+      <c r="MD1" s="1">
+        <v>43763</v>
+      </c>
+      <c r="ME1" s="1">
+        <v>43764</v>
+      </c>
+      <c r="MF1" s="1">
+        <v>43765</v>
+      </c>
+      <c r="MG1" s="1">
+        <v>43766</v>
+      </c>
+      <c r="MH1" s="1">
+        <v>43767</v>
+      </c>
+      <c r="MI1" s="1">
+        <v>43768</v>
+      </c>
+      <c r="MJ1" s="1">
+        <v>43769</v>
+      </c>
+      <c r="MK1" s="3"/>
+      <c r="ML1" s="1">
+        <v>43770</v>
+      </c>
+      <c r="MM1" s="1">
+        <v>43771</v>
+      </c>
+      <c r="MN1" s="1">
+        <v>43772</v>
+      </c>
+      <c r="MO1" s="1">
+        <v>43773</v>
+      </c>
+      <c r="MP1" s="1">
+        <v>43774</v>
+      </c>
+      <c r="MQ1" s="1">
+        <v>43775</v>
+      </c>
+      <c r="MR1" s="1">
+        <v>43776</v>
+      </c>
+      <c r="MS1" s="3"/>
+      <c r="MT1" s="1">
+        <v>43777</v>
+      </c>
+      <c r="MU1" s="1">
+        <v>43778</v>
+      </c>
+      <c r="MV1" s="1">
+        <v>43779</v>
+      </c>
+      <c r="MW1" s="1">
+        <v>43780</v>
+      </c>
+      <c r="MX1" s="1">
+        <v>43781</v>
+      </c>
+      <c r="MY1" s="1">
+        <v>43782</v>
+      </c>
+      <c r="MZ1" s="1">
+        <v>43783</v>
+      </c>
+      <c r="NA1" s="3"/>
+      <c r="NB1" s="1">
+        <v>43784</v>
+      </c>
+      <c r="NC1" s="1">
+        <v>43785</v>
+      </c>
+      <c r="ND1" s="1">
+        <v>43786</v>
+      </c>
+      <c r="NE1" s="1">
+        <v>43787</v>
+      </c>
+      <c r="NF1" s="1">
+        <v>43788</v>
+      </c>
+      <c r="NG1" s="1">
+        <v>43789</v>
+      </c>
+      <c r="NH1" s="1">
+        <v>43790</v>
+      </c>
+      <c r="NI1" s="3"/>
+      <c r="NJ1" s="1">
+        <v>43791</v>
+      </c>
+      <c r="NK1" s="1">
+        <v>43792</v>
+      </c>
+      <c r="NL1" s="1">
+        <v>43793</v>
+      </c>
+      <c r="NM1" s="1">
+        <v>43794</v>
+      </c>
+      <c r="NN1" s="1">
+        <v>43795</v>
+      </c>
+      <c r="NO1" s="1">
+        <v>43796</v>
+      </c>
+      <c r="NP1" s="1">
+        <v>43797</v>
+      </c>
+      <c r="NQ1" s="3"/>
+      <c r="NR1" s="1">
+        <v>43798</v>
+      </c>
+      <c r="NS1" s="1">
+        <v>43799</v>
+      </c>
+      <c r="NT1" s="1">
+        <v>43800</v>
+      </c>
+      <c r="NU1" s="1">
+        <v>43801</v>
+      </c>
+      <c r="NV1" s="1">
+        <v>43802</v>
+      </c>
+      <c r="NW1" s="1">
+        <v>43803</v>
+      </c>
+      <c r="NX1" s="1">
+        <v>43804</v>
+      </c>
+      <c r="NY1" s="3"/>
+      <c r="NZ1" s="1">
+        <v>43805</v>
+      </c>
+      <c r="OA1" s="1">
+        <v>43806</v>
+      </c>
+      <c r="OB1" s="1">
+        <v>43807</v>
+      </c>
+      <c r="OC1" s="1">
+        <v>43808</v>
+      </c>
+      <c r="OD1" s="1">
+        <v>43809</v>
+      </c>
+      <c r="OE1" s="1">
+        <v>43810</v>
+      </c>
+      <c r="OF1" s="1">
+        <v>43811</v>
+      </c>
+      <c r="OG1" s="3"/>
+      <c r="OH1" s="1">
+        <v>43812</v>
+      </c>
+      <c r="OI1" s="1">
+        <v>43813</v>
+      </c>
+      <c r="OJ1" s="1">
+        <v>43814</v>
+      </c>
+      <c r="OK1" s="1">
+        <v>43815</v>
+      </c>
+      <c r="OL1" s="1">
+        <v>43816</v>
+      </c>
+      <c r="OM1" s="1">
+        <v>43817</v>
+      </c>
+      <c r="ON1" s="1">
+        <v>43818</v>
+      </c>
+      <c r="OO1" s="3"/>
+      <c r="OP1" s="1">
+        <v>43819</v>
+      </c>
+      <c r="OQ1" s="1">
+        <v>43820</v>
+      </c>
+      <c r="OR1" s="1">
+        <v>43821</v>
+      </c>
+      <c r="OS1" s="1">
+        <v>43822</v>
+      </c>
+      <c r="OT1" s="1">
+        <v>43823</v>
+      </c>
+      <c r="OU1" s="1">
+        <v>43824</v>
+      </c>
+      <c r="OV1" s="1">
+        <v>43825</v>
+      </c>
+      <c r="OW1" s="3"/>
+      <c r="OX1" s="1">
+        <v>43826</v>
+      </c>
+      <c r="OY1" s="1">
+        <v>43827</v>
+      </c>
+      <c r="OZ1" s="1">
+        <v>43828</v>
+      </c>
+      <c r="PA1" s="1">
+        <v>43829</v>
+      </c>
+      <c r="PB1" s="1">
+        <v>43830</v>
+      </c>
+    </row>
+    <row r="2" spans="2:418" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:418" x14ac:dyDescent="0.3">
+      <c r="B4" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:418" x14ac:dyDescent="0.3">
+      <c r="B5" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:418" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="2:418" x14ac:dyDescent="0.3">
+      <c r="B7" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:418" x14ac:dyDescent="0.3">
+      <c r="B8" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:418" x14ac:dyDescent="0.3">
+      <c r="B9" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="2:418" x14ac:dyDescent="0.3">
+      <c r="B10" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="2:418" x14ac:dyDescent="0.3">
+      <c r="B11" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="2:418" x14ac:dyDescent="0.3">
+      <c r="B12" s="10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/ws.xlsx
+++ b/ws.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="18730"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10709"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jay\Downloads\FALL2017\Caterpillar Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sujayshah/ExcelParsing/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{24E7DCB3-BC1D-7949-9214-1760236AC180}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23016" windowHeight="7236" xr2:uid="{8D38DB33-C587-41A5-A534-4499688D29E5}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="14420" xr2:uid="{8D38DB33-C587-41A5-A534-4499688D29E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -483,162 +484,163 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B9854BD-A2A3-4494-AC62-9F60ECB6DEA5}">
   <dimension ref="B1:PB12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="6" max="423" width="1.77734375" customWidth="1"/>
-    <col min="424" max="424" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="426" max="426" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="428" max="428" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="430" max="430" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="432" max="432" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="434" max="434" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="436" max="436" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="438" max="438" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="440" max="440" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="442" max="442" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="444" max="444" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="446" max="446" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="448" max="448" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="450" max="450" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="452" max="452" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="454" max="454" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="456" max="456" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="458" max="458" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="460" max="460" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="462" max="462" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="464" max="464" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="466" max="466" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="468" max="468" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="470" max="470" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="472" max="472" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="474" max="474" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="476" max="476" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="478" max="478" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="480" max="480" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="482" max="482" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="484" max="484" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="486" max="486" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="488" max="488" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="490" max="490" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="492" max="492" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="494" max="494" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="496" max="496" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="498" max="498" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="500" max="500" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="502" max="502" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="504" max="504" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="506" max="506" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="508" max="508" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="510" max="510" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="512" max="512" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="514" max="514" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="516" max="516" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="518" max="518" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="520" max="520" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="522" max="522" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="524" max="524" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="526" max="526" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="528" max="528" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="530" max="530" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="532" max="532" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="534" max="534" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="536" max="536" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="538" max="538" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="540" max="540" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="542" max="542" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="544" max="544" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="546" max="546" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="548" max="548" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="550" max="550" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="552" max="552" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="554" max="554" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="556" max="556" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="558" max="558" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="560" max="560" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="562" max="562" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="564" max="564" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="566" max="566" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="568" max="568" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="570" max="570" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="572" max="572" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="574" max="574" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="576" max="576" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="578" max="578" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="580" max="580" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="582" max="582" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="584" max="584" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="586" max="586" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="588" max="588" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="590" max="590" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="592" max="592" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="594" max="594" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="596" max="596" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="598" max="598" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="600" max="600" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="602" max="602" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="604" max="604" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="606" max="606" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="608" max="608" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="610" max="610" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="612" max="612" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="614" max="614" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="616" max="616" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="618" max="618" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="620" max="620" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="622" max="622" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="624" max="624" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="626" max="626" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="628" max="628" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="630" max="630" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="632" max="632" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="634" max="634" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="636" max="636" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="638" max="638" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="640" max="640" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="642" max="642" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="644" max="644" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="646" max="646" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="648" max="648" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="650" max="650" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="652" max="652" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="654" max="654" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="656" max="656" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="658" max="658" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="660" max="660" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="662" max="662" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="664" max="664" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="666" max="666" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="668" max="668" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="670" max="670" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="672" max="672" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="674" max="674" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="676" max="676" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="678" max="678" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="680" max="680" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="682" max="682" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="684" max="684" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="686" max="686" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="688" max="688" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="690" max="690" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="692" max="692" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="694" max="694" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="696" max="696" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="698" max="698" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="700" max="700" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="702" max="702" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="704" max="704" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="706" max="706" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="708" max="708" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="710" max="710" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="712" max="712" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="714" max="714" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="716" max="716" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="718" max="718" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="720" max="720" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="722" max="722" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="49" customWidth="1"/>
+    <col min="6" max="423" width="1.83203125" customWidth="1"/>
+    <col min="424" max="424" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="426" max="426" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="428" max="428" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="430" max="430" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="432" max="432" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="434" max="434" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="436" max="436" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="438" max="438" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="440" max="440" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="442" max="442" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="444" max="444" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="446" max="446" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="448" max="448" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="450" max="450" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="452" max="452" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="454" max="454" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="456" max="456" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="458" max="458" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="460" max="460" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="462" max="462" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="464" max="464" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="466" max="466" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="468" max="468" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="470" max="470" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="472" max="472" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="474" max="474" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="476" max="476" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="478" max="478" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="480" max="480" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="482" max="482" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="484" max="484" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="486" max="486" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="488" max="488" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="490" max="490" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="492" max="492" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="494" max="494" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="496" max="496" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="498" max="498" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="500" max="500" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="502" max="502" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="504" max="504" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="506" max="506" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="508" max="508" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="510" max="510" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="512" max="512" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="514" max="514" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="516" max="516" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="518" max="518" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="520" max="520" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="522" max="522" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="524" max="524" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="526" max="526" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="528" max="528" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="530" max="530" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="532" max="532" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="534" max="534" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="536" max="536" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="538" max="538" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="540" max="540" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="542" max="542" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="544" max="544" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="546" max="546" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="548" max="548" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="550" max="550" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="552" max="552" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="554" max="554" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="556" max="556" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="558" max="558" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="560" max="560" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="562" max="562" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="564" max="564" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="566" max="566" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="568" max="568" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="570" max="570" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="572" max="572" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="574" max="574" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="576" max="576" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="578" max="578" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="580" max="580" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="582" max="582" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="584" max="584" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="586" max="586" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="588" max="588" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="590" max="590" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="592" max="592" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="594" max="594" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="596" max="596" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="598" max="598" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="600" max="600" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="602" max="602" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="604" max="604" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="606" max="606" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="608" max="608" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="610" max="610" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="612" max="612" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="614" max="614" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="616" max="616" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="618" max="618" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="620" max="620" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="622" max="622" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="624" max="624" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="626" max="626" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="628" max="628" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="630" max="630" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="632" max="632" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="634" max="634" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="636" max="636" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="638" max="638" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="640" max="640" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="642" max="642" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="644" max="644" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="646" max="646" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="648" max="648" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="650" max="650" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="652" max="652" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="654" max="654" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="656" max="656" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="658" max="658" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="660" max="660" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="662" max="662" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="664" max="664" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="666" max="666" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="668" max="668" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="670" max="670" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="672" max="672" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="674" max="674" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="676" max="676" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="678" max="678" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="680" max="680" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="682" max="682" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="684" max="684" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="686" max="686" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="688" max="688" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="690" max="690" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="692" max="692" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="694" max="694" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="696" max="696" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="698" max="698" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="700" max="700" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="702" max="702" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="704" max="704" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="706" max="706" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="708" max="708" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="710" max="710" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="712" max="712" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="714" max="714" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="716" max="716" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="718" max="718" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="720" max="720" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="722" max="722" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:418" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:418" x14ac:dyDescent="0.2">
       <c r="C1" t="s">
         <v>10</v>
       </c>
@@ -1783,52 +1785,52 @@
         <v>43830</v>
       </c>
     </row>
-    <row r="2" spans="2:418" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:418" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:418" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:418" x14ac:dyDescent="0.2">
       <c r="B4" s="11" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:418" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:418" x14ac:dyDescent="0.2">
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:418" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:418" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="2:418" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:418" x14ac:dyDescent="0.2">
       <c r="B7" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="2:418" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:418" x14ac:dyDescent="0.2">
       <c r="B8" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:418" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:418" x14ac:dyDescent="0.2">
       <c r="B9" s="7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="2:418" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:418" x14ac:dyDescent="0.2">
       <c r="B10" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="2:418" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:418" x14ac:dyDescent="0.2">
       <c r="B11" s="9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="2:418" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:418" x14ac:dyDescent="0.2">
       <c r="B12" s="10" t="s">
         <v>9</v>
       </c>
